--- a/tmp/프로젝트 제출양식/2. 프로젝트 결과 보고서/20260428_유스케이스.xlsx
+++ b/tmp/프로젝트 제출양식/2. 프로젝트 결과 보고서/20260428_유스케이스.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Desktop\HAYUL\eclipse\ShoppingMall\tmp\프로젝트 제출양식\2. 프로젝트 결과 보고서\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20400" windowHeight="8970"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12165"/>
   </bookViews>
   <sheets>
     <sheet name="20260428_유스케이스 다이어그램" sheetId="1" r:id="rId1"/>
